--- a/currentbuild/StructureDefinition-NoBasisPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-NoBasisPractitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.2</t>
+    <t>0.8.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T06:42:57+00:00</t>
+    <t>2024-03-15T09:00:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-NoBasisPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-NoBasisPractitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.3</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-15T09:00:42+00:00</t>
+    <t>2024-03-17T09:59:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-NoBasisPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-NoBasisPractitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-17T09:59:20+00:00</t>
+    <t>2024-04-06T16:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>HL7 Norway (https://github.com/HL7Norway)</t>
   </si>
   <si>
     <t>Description</t>

--- a/currentbuild/StructureDefinition-NoBasisPractitioner.xlsx
+++ b/currentbuild/StructureDefinition-NoBasisPractitioner.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-06T16:49:55+00:00</t>
+    <t>2024-04-28T16:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
